--- a/data/trans_bre/P16A04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,65</t>
+          <t>-1,97; 0,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,73</t>
+          <t>-2,48; 0,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,25</t>
+          <t>-0,24; 2,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,01</t>
+          <t>-1,0; 3,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,33; 29,36</t>
+          <t>-52,01; 29,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,64; 31,49</t>
+          <t>-54,14; 29,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 290,13</t>
+          <t>-22,43; 313,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 150,04</t>
+          <t>-21,62; 125,6</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,9</t>
+          <t>0,03; 1,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,74</t>
+          <t>-0,53; 1,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,65</t>
+          <t>-0,98; 0,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,49</t>
+          <t>-0,64; 1,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 204,36</t>
+          <t>-5,75; 194,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 78,76</t>
+          <t>-17,1; 90,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 39,87</t>
+          <t>-37,27; 48,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 95,43</t>
+          <t>-24,0; 93,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,68</t>
+          <t>-0,8; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,58</t>
+          <t>-2,43; 1,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,22</t>
+          <t>-2,0; 2,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,41</t>
+          <t>-0,03; 2,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,39; 515,78</t>
+          <t>-71,98; 640,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-79,27; 217,37</t>
+          <t>-81,19; 234,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,61; 147,21</t>
+          <t>-57,16; 128,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 350,42</t>
+          <t>-20,01; 326,59</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,2</t>
+          <t>-0,25; 1,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,82</t>
+          <t>-0,93; 0,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,88</t>
+          <t>-0,49; 0,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,69</t>
+          <t>0,04; 1,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 80,16</t>
+          <t>-12,04; 76,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 32,07</t>
+          <t>-28,77; 35,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 52,1</t>
+          <t>-20,4; 54,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 97,27</t>
+          <t>1,01; 105,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,69</t>
+          <t>-1,98; 0,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,69</t>
+          <t>-2,28; 0,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,27</t>
+          <t>-0,09; 2,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,76</t>
+          <t>-0,88; 2,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,01; 29,6</t>
+          <t>-50,81; 32,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 29,7</t>
+          <t>-54,44; 29,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 313,11</t>
+          <t>-10,08; 364,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 125,6</t>
+          <t>-18,39; 110,29</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,8</t>
+          <t>0,06; 1,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,93</t>
+          <t>-0,57; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,83</t>
+          <t>-0,99; 0,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,41</t>
+          <t>-0,43; 1,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 194,97</t>
+          <t>-0,54; 189,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 90,36</t>
+          <t>-19,88; 85,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 48,8</t>
+          <t>-38,52; 47,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 93,38</t>
+          <t>-14,96; 80,75</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>154,62%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,64</t>
+          <t>-0,79; 1,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,57</t>
+          <t>-2,34; 1,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,02</t>
+          <t>-1,81; 2,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,45</t>
+          <t>0,38; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,98; 640,39</t>
+          <t>-66,21; 586,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-81,19; 234,01</t>
+          <t>-81,98; 157,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,16; 128,52</t>
+          <t>-52,2; 161,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 326,59</t>
+          <t>13,18; 553,63</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,1</t>
+          <t>-0,29; 1,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,86</t>
+          <t>-0,86; 0,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,93</t>
+          <t>-0,49; 0,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,79</t>
+          <t>0,17; 1,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 76,57</t>
+          <t>-14,59; 76,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 35,09</t>
+          <t>-27,3; 35,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 54,14</t>
+          <t>-20,86; 55,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 105,18</t>
+          <t>5,49; 87,16</t>
         </is>
       </c>
     </row>
